--- a/Pasta1.xlsx
+++ b/Pasta1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno.GR-D-DL-13.000\Documents\GitHub\AnaRaquel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BDC0AD-B7E2-4579-A0E3-CD6BEB933D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B442ABF-0D8F-48C2-8F56-EA0B88BCBA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="0" windowWidth="21600" windowHeight="15585" xr2:uid="{450EDCDD-FBD0-498F-B32B-64E5E8D32A21}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28500" windowHeight="11295" xr2:uid="{450EDCDD-FBD0-498F-B32B-64E5E8D32A21}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -127,14 +127,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -142,15 +139,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,28 +463,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D027D5-3A7A-4EDC-9F76-B32D8F97FAB2}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="7" customFormat="1" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
@@ -506,74 +499,56 @@
       <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
     </row>
-    <row r="3" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:8" s="8" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>52000</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>48000</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>51000</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>50000</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>47000</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>49000</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:8" s="8" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>31500</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>29000</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>30000</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>31000</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>30000</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>31000</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
